--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA312"/>
+  <dimension ref="A1:AA316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34816,6 +34816,390 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Funkd Up Wines As</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Funkd Up Wines As</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>126224</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>14b Linneaveien</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>https://funkdupwines.com</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr"/>
+      <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr"/>
+      <c r="M313" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N313" s="2" t="inlineStr">
+        <is>
+          <t>shizzle@funkdupwines.com</t>
+        </is>
+      </c>
+      <c r="O313" s="2" t="inlineStr"/>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr"/>
+      <c r="R313" s="2" t="inlineStr"/>
+      <c r="S313" s="2" t="inlineStr"/>
+      <c r="T313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr">
+        <is>
+          <t>Kim Gregorio</t>
+        </is>
+      </c>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>145826</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Bodø</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Nordland</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>13 Burøyveien</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matgrossisten.com</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@sjule.no</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>+47 75 19 88 88</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>923623019</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr"/>
+      <c r="S314" s="2" t="inlineStr"/>
+      <c r="T314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr">
+        <is>
+          <t>Hilde Mollevik</t>
+        </is>
+      </c>
+      <c r="X314" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>145826</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Bodø</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Nordland</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>13 Burøyveien</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matgrossisten.com</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr"/>
+      <c r="K315" s="2" t="inlineStr"/>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N315" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@sjule.no</t>
+        </is>
+      </c>
+      <c r="O315" s="2" t="inlineStr">
+        <is>
+          <t>+47 75 19 88 88</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>923623019</t>
+        </is>
+      </c>
+      <c r="R315" s="2" t="inlineStr"/>
+      <c r="S315" s="2" t="inlineStr"/>
+      <c r="T315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr"/>
+      <c r="W315" s="2" t="inlineStr">
+        <is>
+          <t>Astrid Kristiansen</t>
+        </is>
+      </c>
+      <c r="X315" s="2" t="inlineStr">
+        <is>
+          <t>Office Manager</t>
+        </is>
+      </c>
+      <c r="Y315" s="2" t="inlineStr"/>
+      <c r="Z315" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>145826</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Bodø</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Nordland</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>13 Burøyveien</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matgrossisten.com</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr"/>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@sjule.no</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr">
+        <is>
+          <t>+47 75 19 88 88</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>923623019</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="inlineStr"/>
+      <c r="S316" s="2" t="inlineStr"/>
+      <c r="T316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr"/>
+      <c r="W316" s="2" t="inlineStr">
+        <is>
+          <t>Trygve Larsen</t>
+        </is>
+      </c>
+      <c r="X316" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y316" s="2" t="inlineStr"/>
+      <c r="Z316" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA316" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA316"/>
+  <dimension ref="A1:AA322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35200,6 +35200,600 @@
       </c>
       <c r="AA316" s="2" t="inlineStr"/>
     </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Oslo Wine Agency As</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>Oslo Wine Agency As</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>42535</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novabeveragegroup.no, https://www.oslowineagency.no</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr"/>
+      <c r="K317" s="2" t="inlineStr"/>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>post@oslowineagency.no</t>
+        </is>
+      </c>
+      <c r="O317" s="2" t="inlineStr"/>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>917214697</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eurowine-as/</t>
+        </is>
+      </c>
+      <c r="S317" s="2" t="inlineStr"/>
+      <c r="T317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr"/>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t>Martin Tobiasson</t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-tobiasson-b66986a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Oslo Wine Agency As</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Oslo Wine Agency As</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>42535</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.novabeveragegroup.no, https://www.oslowineagency.no</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr"/>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>post@oslowineagency.no</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr"/>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>917214697</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eurowine-as/</t>
+        </is>
+      </c>
+      <c r="S318" s="2" t="inlineStr"/>
+      <c r="T318" s="2" t="inlineStr"/>
+      <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr"/>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>Marianne Monin</t>
+        </is>
+      </c>
+      <c r="X318" s="2" t="inlineStr">
+        <is>
+          <t>Product And Quality Manager</t>
+        </is>
+      </c>
+      <c r="Y318" s="2" t="inlineStr"/>
+      <c r="Z318" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marianne-monin-b4135854/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Funkd Up Wines As</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Funkd Up Wines As</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>126224</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>14b Linneaveien</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>https://funkdupwines.com</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr"/>
+      <c r="K319" s="2" t="inlineStr"/>
+      <c r="L319" s="2" t="inlineStr"/>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>shizzle@funkdupwines.com</t>
+        </is>
+      </c>
+      <c r="O319" s="2" t="inlineStr"/>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q319" s="2" t="inlineStr"/>
+      <c r="R319" s="2" t="inlineStr"/>
+      <c r="S319" s="2" t="inlineStr"/>
+      <c r="T319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr"/>
+      <c r="W319" s="2" t="inlineStr">
+        <is>
+          <t>Kim Gregorio</t>
+        </is>
+      </c>
+      <c r="X319" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y319" s="2" t="inlineStr"/>
+      <c r="Z319" s="2" t="inlineStr"/>
+      <c r="AA319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>145826</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Bodø</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Nordland</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>13 Burøyveien</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matgrossisten.com</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr"/>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@sjule.no</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>+47 75 19 88 88</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>923623019</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="inlineStr"/>
+      <c r="S320" s="2" t="inlineStr"/>
+      <c r="T320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr"/>
+      <c r="W320" s="2" t="inlineStr">
+        <is>
+          <t>Hilde Mollevik</t>
+        </is>
+      </c>
+      <c r="X320" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y320" s="2" t="inlineStr"/>
+      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="AA320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>145826</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Bodø</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Nordland</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>13 Burøyveien</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matgrossisten.com</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr"/>
+      <c r="K321" s="2" t="inlineStr"/>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@sjule.no</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>+47 75 19 88 88</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>923623019</t>
+        </is>
+      </c>
+      <c r="R321" s="2" t="inlineStr"/>
+      <c r="S321" s="2" t="inlineStr"/>
+      <c r="T321" s="2" t="inlineStr"/>
+      <c r="U321" s="2" t="inlineStr"/>
+      <c r="V321" s="2" t="inlineStr"/>
+      <c r="W321" s="2" t="inlineStr">
+        <is>
+          <t>Astrid Kristiansen</t>
+        </is>
+      </c>
+      <c r="X321" s="2" t="inlineStr">
+        <is>
+          <t>Office Manager</t>
+        </is>
+      </c>
+      <c r="Y321" s="2" t="inlineStr"/>
+      <c r="Z321" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>Matgrossisten As</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>145826</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Bodø</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Nordland</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>13 Burøyveien</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.matgrossisten.com</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@sjule.no</t>
+        </is>
+      </c>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>+47 75 19 88 88</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>923623019</t>
+        </is>
+      </c>
+      <c r="R322" s="2" t="inlineStr"/>
+      <c r="S322" s="2" t="inlineStr"/>
+      <c r="T322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="inlineStr"/>
+      <c r="W322" s="2" t="inlineStr">
+        <is>
+          <t>Trygve Larsen</t>
+        </is>
+      </c>
+      <c r="X322" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y322" s="2" t="inlineStr"/>
+      <c r="Z322" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA322" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA322"/>
+  <dimension ref="A1:AA334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35794,6 +35794,1186 @@
       </c>
       <c r="AA322" s="2" t="inlineStr"/>
     </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>World Seasonal Tasting As</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>World Seasonal Tasting As</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>145792</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Kristiansand</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Agder</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>26 Holdalsnuten</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://worldseasonaltasting.com</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr"/>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>info@worldseasonaltasting.com</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr"/>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>927215160</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr"/>
+      <c r="S323" s="2" t="inlineStr"/>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/worldseasonaltasting/</t>
+        </is>
+      </c>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr">
+        <is>
+          <t>Øystein Haugen</t>
+        </is>
+      </c>
+      <c r="X323" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y323" s="2" t="inlineStr"/>
+      <c r="Z323" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%C3%B8ystein-haugen-84b01141</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>World Seasonal Tasting As</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>World Seasonal Tasting As</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>145792</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Kristiansand</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>Agder</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>26 Holdalsnuten</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>https://worldseasonaltasting.com</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>info@worldseasonaltasting.com</t>
+        </is>
+      </c>
+      <c r="O324" s="2" t="inlineStr"/>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>927215160</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="inlineStr"/>
+      <c r="S324" s="2" t="inlineStr"/>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/worldseasonaltasting/</t>
+        </is>
+      </c>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Castro</t>
+        </is>
+      </c>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>Coo</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="AA324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Vinima As</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>Vinima As</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>145794</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>https://vinima.no</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr"/>
+      <c r="K325" s="2" t="inlineStr"/>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr">
+        <is>
+          <t>ole.steinsholt@vinima.no</t>
+        </is>
+      </c>
+      <c r="O325" s="2" t="inlineStr"/>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>998913543</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinima-as/</t>
+        </is>
+      </c>
+      <c r="S325" s="2" t="inlineStr"/>
+      <c r="T325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinimawines/</t>
+        </is>
+      </c>
+      <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr">
+        <is>
+          <t>Ole Steinsholt</t>
+        </is>
+      </c>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Partner</t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr"/>
+      <c r="Z325" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ole-steinsholt-05658932/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Vinima As</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>Vinima As</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>145794</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://vinima.no</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr"/>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>ole.steinsholt@vinima.no</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr"/>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>998913543</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinima-as/</t>
+        </is>
+      </c>
+      <c r="S326" s="2" t="inlineStr"/>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinimawines/</t>
+        </is>
+      </c>
+      <c r="U326" s="2" t="inlineStr"/>
+      <c r="V326" s="2" t="inlineStr"/>
+      <c r="W326" s="2" t="inlineStr">
+        <is>
+          <t>Christian Almstrøm</t>
+        </is>
+      </c>
+      <c r="X326" s="2" t="inlineStr">
+        <is>
+          <t>Product And Marketing/ Partner</t>
+        </is>
+      </c>
+      <c r="Y326" s="2" t="inlineStr"/>
+      <c r="Z326" s="2" t="inlineStr"/>
+      <c r="AA326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christian-almstrom-921b3a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Wevinos As</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>Wevinos As</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>145796</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Sandbakk</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>97 Lutsiveien</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wevinos.com</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr"/>
+      <c r="K327" s="2" t="inlineStr"/>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>Kontakt@wevinos.com</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr"/>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>932047373</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr"/>
+      <c r="S327" s="2" t="inlineStr"/>
+      <c r="T327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr">
+        <is>
+          <t>Svein Leon</t>
+        </is>
+      </c>
+      <c r="X327" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr"/>
+      <c r="AA327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Wevinos As</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Wevinos As</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>145796</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Sandbakk</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>97 Lutsiveien</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wevinos.com</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr"/>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>Kontakt@wevinos.com</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr"/>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>932047373</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr"/>
+      <c r="S328" s="2" t="inlineStr"/>
+      <c r="T328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>Hilde Danielsen</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr"/>
+      <c r="Z328" s="2" t="inlineStr"/>
+      <c r="AA328" s="2" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Wine-oh As</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Wine-oh As</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>145798</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>83 Bretlandsgata</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>https://wine-oh.no</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr"/>
+      <c r="K329" s="2" t="inlineStr"/>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>janne@wine-oh.no</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr"/>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>916524684</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr"/>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/wineoh.no</t>
+        </is>
+      </c>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/wine_oh.no</t>
+        </is>
+      </c>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr"/>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>Janne Paula</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr"/>
+      <c r="AA329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>Wine-oh As</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>Wine-oh As</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>145798</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>83 Bretlandsgata</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://wine-oh.no</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr"/>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>janne@wine-oh.no</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr"/>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>916524684</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr"/>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/wineoh.no</t>
+        </is>
+      </c>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/wine_oh.no</t>
+        </is>
+      </c>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr"/>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>Marianne Martens</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr"/>
+      <c r="Z330" s="2" t="inlineStr"/>
+      <c r="AA330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Moswines As</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>Moswines As</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>39119</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>Vendelåsen 8</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://moswines.no</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr"/>
+      <c r="K331" s="2" t="inlineStr"/>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>pal@moswines.no</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr"/>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>912321304</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr"/>
+      <c r="S331" s="2" t="inlineStr"/>
+      <c r="T331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr"/>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>Pål Mosbergvik</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>Ceo And Owner</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr"/>
+      <c r="AA331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/p%c3%a5l-mosbergvik-6753851/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VCT Norway AS </t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VCT Norway AS </t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>45101</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>4 Karenslyst Allé</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>0278</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://vctnorway.com</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr"/>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>heidi.stumo@vctnorway.com</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>+47 23 08 38 70</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>993253391</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr"/>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/conchaytoro.norway</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vctnorway/</t>
+        </is>
+      </c>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr"/>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>Heidi Stumo</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/heidi-stumo-7858b19/?originalSubdomain=no</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VCT Norway AS </t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VCT Norway AS </t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>45101</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>4 Karenslyst Allé</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>0278</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://vctnorway.com</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr"/>
+      <c r="K333" s="2" t="inlineStr"/>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>heidi.stumo@vctnorway.com</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>+47 23 08 38 70</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>993253391</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr"/>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/conchaytoro.norway</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vctnorway/</t>
+        </is>
+      </c>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>Kine Rasmussen</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr"/>
+      <c r="Z333" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kine-rasmussen-7738a773/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Regala As</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Regala As</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>145616</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Trøndelag</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>7 Kjøpmannsgata</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>7013</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://regala.no</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>post@regala.no</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr"/>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>989029037</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr"/>
+      <c r="S334" s="2" t="inlineStr"/>
+      <c r="T334" s="2" t="inlineStr"/>
+      <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr"/>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Martin</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr"/>
+      <c r="Z334" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-wiggen-451804121/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA334"/>
+  <dimension ref="A1:AA340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36974,6 +36974,544 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Sorellina As</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Sorellina As</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>145801</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>54 Jacob Aalls gate</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>0364</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://sorellina.no</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr"/>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>info@sorellina.no</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr"/>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>922336261</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr"/>
+      <c r="S335" s="2" t="inlineStr"/>
+      <c r="T335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>Jørgen Ljøstad</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr"/>
+      <c r="AA335" s="2" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Sorellina As</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Sorellina As</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>145801</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>54 Jacob Aalls gate</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>0364</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://sorellina.no</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>info@sorellina.no</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr"/>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>922336261</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr"/>
+      <c r="S336" s="2" t="inlineStr"/>
+      <c r="T336" s="2" t="inlineStr"/>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr"/>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>Pål Kvernaas</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr"/>
+      <c r="AA336" s="2" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Scent Hound As</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Scent Hound As</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>145808</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>61 Vækerøveien</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>0382</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.scenthoundcellars.com</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr"/>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>info@scenthoundcellars.com</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr"/>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>916801688</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr"/>
+      <c r="S337" s="2" t="inlineStr"/>
+      <c r="T337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr"/>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t>Vincent Tomas</t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Think Liquid As</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Think Liquid As</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>145800</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>8 Schæffers gate</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>0558</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://thinkliquid.no</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>INFO@THINKLIQUID.NO</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr"/>
+      <c r="P338" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>931615297</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr"/>
+      <c r="S338" s="2" t="inlineStr"/>
+      <c r="T338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Piras</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Weingut As</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Weingut As</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>145797</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>28 Melumveien</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>0760</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://weingut.no</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>jens.frydenlund@weingut.no</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr"/>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>931026259</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr"/>
+      <c r="S339" s="2" t="inlineStr"/>
+      <c r="T339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>Jens Frydenlund</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jens-frydenlund</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Bymunk Aps</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Bymunk Aps</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>35613</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Drøbak</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>1 Havnebakken</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://gaverogvin.dk</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr"/>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>info@gaverogvin.dk</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>+45 20 66 22 29</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>36478330</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kandis-gaver-vin</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KandisRy</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr"/>
+      <c r="X340" s="2" t="inlineStr"/>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA340"/>
+  <dimension ref="A1:AA349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37512,6 +37512,931 @@
       <c r="Z340" s="2" t="inlineStr"/>
       <c r="AA340" s="2" t="inlineStr"/>
     </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Norvin As</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Norvin As</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>145824</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Lysaker</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Viken</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>Lysaker brygge 27</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://norvinbeverage.com</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr"/>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>info@norvin.no</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 44 73 00</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>919339985</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr"/>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/NorvinNorge/</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>Christian Algreen Berger</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Nafstad As</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Nafstad As</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>145822</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>35 Munkedamsveien</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nafstad-as.no</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>bestilling@nafstad-as.no</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 83 30 10</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>978690211</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr"/>
+      <c r="S342" s="2" t="inlineStr"/>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nafstad_like_fine_wine/</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr">
+        <is>
+          <t>Halvor Nafstad</t>
+        </is>
+      </c>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA342" s="2" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Nafstad As</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Nafstad As</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>145822</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>35 Munkedamsveien</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nafstad-as.no</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>bestilling@nafstad-as.no</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 83 30 10</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>978690211</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr"/>
+      <c r="S343" s="2" t="inlineStr"/>
+      <c r="T343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nafstad_like_fine_wine/</t>
+        </is>
+      </c>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>Siri Nafstad</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA343" s="2" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>145851</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>60 Parkveien</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>0254</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>https://bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>post@bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr"/>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>914981654</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bona-fide-wines/</t>
+        </is>
+      </c>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Bona-Fide-Wines-61555836004913/</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonafidewines_norway/</t>
+        </is>
+      </c>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr">
+        <is>
+          <t>Gunnar Skoglund</t>
+        </is>
+      </c>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gunnarskoglund</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>145851</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>60 Parkveien</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>0254</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>post@bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr"/>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>914981654</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bona-fide-wines/</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Bona-Fide-Wines-61555836004913/</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonafidewines_norway/</t>
+        </is>
+      </c>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>Scott Casban</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-casban-97868298</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>145851</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>60 Parkveien</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>0254</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>post@bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr"/>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>914981654</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bona-fide-wines/</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Bona-Fide-Wines-61555836004913/</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonafidewines_norway/</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Johansson</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-johansson-501721126</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Bona Fide Wines As</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>145851</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>60 Parkveien</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>0254</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>post@bonafidewines.no</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr"/>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>914981654</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bona-fide-wines/</t>
+        </is>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Bona-Fide-Wines-61555836004913/</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonafidewines_norway/</t>
+        </is>
+      </c>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Grette</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Co-founder &amp; Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-grette-a567933/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>Gourmet Wines As</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Gourmet Wines As</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>145835</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>6 Neslia</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>https://gourmetwines.no</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr"/>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr"/>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>info@gourmetwines.no</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr"/>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>923309926</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr"/>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/Gourmet-Wines-106703064216462</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="inlineStr"/>
+      <c r="V348" s="2" t="inlineStr"/>
+      <c r="W348" s="2" t="inlineStr">
+        <is>
+          <t>Helene Libæk</t>
+        </is>
+      </c>
+      <c r="X348" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/helenel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>Grappolo As</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Grappolo As</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>145832</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>73 Grefsenveien</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>0487</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.grappolo.no</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr"/>
+      <c r="K349" s="2" t="inlineStr"/>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr"/>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>mail@grappolo.no</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr"/>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>998310083</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr"/>
+      <c r="S349" s="2" t="inlineStr"/>
+      <c r="T349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grappolo.no/</t>
+        </is>
+      </c>
+      <c r="U349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="inlineStr"/>
+      <c r="W349" s="2" t="inlineStr">
+        <is>
+          <t>Alex Bruvoll</t>
+        </is>
+      </c>
+      <c r="X349" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y349" s="2" t="inlineStr"/>
+      <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-bruvoll-9a5235a6/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA349"/>
+  <dimension ref="A1:AA362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -38437,6 +38437,1255 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr"/>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr"/>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr"/>
+      <c r="S350" s="2" t="inlineStr"/>
+      <c r="T350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr"/>
+      <c r="W350" s="2" t="inlineStr">
+        <is>
+          <t>Richard Eikeland</t>
+        </is>
+      </c>
+      <c r="X350" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Logistics</t>
+        </is>
+      </c>
+      <c r="Y350" s="2" t="inlineStr"/>
+      <c r="Z350" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr"/>
+      <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="inlineStr"/>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr"/>
+      <c r="P351" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="inlineStr"/>
+      <c r="S351" s="2" t="inlineStr"/>
+      <c r="T351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr"/>
+      <c r="W351" s="2" t="inlineStr">
+        <is>
+          <t>Peter Dorstad</t>
+        </is>
+      </c>
+      <c r="X351" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Product Manager</t>
+        </is>
+      </c>
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-d%C3%B8rstad-526782138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>145830</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Viken</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>5 Orreveien</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>0789</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.interlope.no</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr"/>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>wine@interlope.no</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 49 02 20</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>998058929</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr"/>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/interlope.wine/</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="inlineStr"/>
+      <c r="V352" s="2" t="inlineStr"/>
+      <c r="W352" s="2" t="inlineStr">
+        <is>
+          <t>Ingar Grønstad</t>
+        </is>
+      </c>
+      <c r="X352" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y352" s="2" t="inlineStr"/>
+      <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr"/>
+      <c r="K353" s="2" t="inlineStr"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr"/>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr"/>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S353" s="2" t="inlineStr"/>
+      <c r="T353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U353" s="2" t="inlineStr"/>
+      <c r="V353" s="2" t="inlineStr"/>
+      <c r="W353" s="2" t="inlineStr">
+        <is>
+          <t>Giacomo Caramaschi</t>
+        </is>
+      </c>
+      <c r="X353" s="2" t="inlineStr">
+        <is>
+          <t>Co-Owner</t>
+        </is>
+      </c>
+      <c r="Y353" s="2" t="inlineStr"/>
+      <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr"/>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S354" s="2" t="inlineStr"/>
+      <c r="T354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Colsenet</t>
+        </is>
+      </c>
+      <c r="X354" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Co-owner</t>
+        </is>
+      </c>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benjamin-colsenet-34bb472b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr"/>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr"/>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr"/>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S355" s="2" t="inlineStr"/>
+      <c r="T355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan D. Roth</t>
+        </is>
+      </c>
+      <c r="X355" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>145823</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>https://larssoreide.no</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>post@larssoreide.no</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr"/>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>945663855</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr"/>
+      <c r="S356" s="2" t="inlineStr"/>
+      <c r="T356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lars-s%C3%B8reide-393732174/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr"/>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr"/>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr"/>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr"/>
+      <c r="S357" s="2" t="inlineStr"/>
+      <c r="T357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr">
+        <is>
+          <t>Jan Erik</t>
+        </is>
+      </c>
+      <c r="X357" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr"/>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr"/>
+      <c r="S358" s="2" t="inlineStr"/>
+      <c r="T358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr">
+        <is>
+          <t>Simen Syrrist</t>
+        </is>
+      </c>
+      <c r="X358" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>145839</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>6A Veitvetveien</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>0596</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr"/>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr"/>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>import@chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr"/>
+      <c r="P359" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>932088525</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr"/>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61552797656796</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chrismidtunimport</t>
+        </is>
+      </c>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun</t>
+        </is>
+      </c>
+      <c r="X359" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr"/>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr"/>
+      <c r="P360" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="inlineStr"/>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr"/>
+      <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr">
+        <is>
+          <t>Pål Bertil</t>
+        </is>
+      </c>
+      <c r="X360" s="2" t="inlineStr">
+        <is>
+          <t>Chairman And Owner</t>
+        </is>
+      </c>
+      <c r="Y360" s="2" t="inlineStr"/>
+      <c r="Z360" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/p%C3%A5l-bertil-eide-69414610b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr"/>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr"/>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr"/>
+      <c r="P361" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="inlineStr"/>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="inlineStr"/>
+      <c r="W361" s="2" t="inlineStr">
+        <is>
+          <t>Olav Martens</t>
+        </is>
+      </c>
+      <c r="X361" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y361" s="2" t="inlineStr"/>
+      <c r="Z361" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/olav-martens-solli-2b0221121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>102275</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>134 Randabergveien</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>http://www.terroir.no</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr"/>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>torleiv@terroir.no</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr"/>
+      <c r="P362" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>976307356</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="inlineStr"/>
+      <c r="S362" s="2" t="inlineStr"/>
+      <c r="T362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="inlineStr"/>
+      <c r="V362" s="2" t="inlineStr"/>
+      <c r="W362" s="2" t="inlineStr">
+        <is>
+          <t>Torleiv B.</t>
+        </is>
+      </c>
+      <c r="X362" s="2" t="inlineStr">
+        <is>
+          <t>Owner, Ceo</t>
+        </is>
+      </c>
+      <c r="Y362" s="2" t="inlineStr"/>
+      <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/torleiv-middelthon-81101528/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA362"/>
+  <dimension ref="A1:AA379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39686,6 +39686,1663 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>145850</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>2 Gustavs gate</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dogowines.com</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr"/>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr"/>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>danjoakim@dogowines.no</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr"/>
+      <c r="P363" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>926421867</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr"/>
+      <c r="S363" s="2" t="inlineStr"/>
+      <c r="T363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dogowines/</t>
+        </is>
+      </c>
+      <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr"/>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>Dan Joakim</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dan-joakim-ask-nessa-0918171b</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr"/>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr">
+        <is>
+          <t>Dag Robert</t>
+        </is>
+      </c>
+      <c r="X364" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dag-robert-s%C3%B8r%C3%A5s-077aa3a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr"/>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr">
+        <is>
+          <t>Carl Frimanslund</t>
+        </is>
+      </c>
+      <c r="X365" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carl-frimanslund/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>45175</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Sandvika</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>2A Jongsåsveien</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>espen@bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr"/>
+      <c r="P366" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>922253935</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="inlineStr"/>
+      <c r="S366" s="2" t="inlineStr"/>
+      <c r="T366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr">
+        <is>
+          <t>Espen Hoel</t>
+        </is>
+      </c>
+      <c r="X366" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/espen-hoel-80494a3b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr"/>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr"/>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr"/>
+      <c r="P367" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr"/>
+      <c r="S367" s="2" t="inlineStr"/>
+      <c r="T367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr"/>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>Richard Eikeland</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Logistics</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr"/>
+      <c r="P368" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr"/>
+      <c r="S368" s="2" t="inlineStr"/>
+      <c r="T368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr"/>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>Peter Dorstad</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Product Manager</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-d%C3%B8rstad-526782138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>145830</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Viken</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>5 Orreveien</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>0789</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.interlope.no</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr"/>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>wine@interlope.no</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 49 02 20</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>998058929</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr"/>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/interlope.wine/</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr">
+        <is>
+          <t>Ingar Grønstad</t>
+        </is>
+      </c>
+      <c r="X369" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr"/>
+      <c r="P370" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S370" s="2" t="inlineStr"/>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr">
+        <is>
+          <t>Giacomo Caramaschi</t>
+        </is>
+      </c>
+      <c r="X370" s="2" t="inlineStr">
+        <is>
+          <t>Co-Owner</t>
+        </is>
+      </c>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr"/>
+      <c r="P371" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S371" s="2" t="inlineStr"/>
+      <c r="T371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Colsenet</t>
+        </is>
+      </c>
+      <c r="X371" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Co-owner</t>
+        </is>
+      </c>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benjamin-colsenet-34bb472b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr"/>
+      <c r="P372" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S372" s="2" t="inlineStr"/>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr"/>
+      <c r="W372" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan D. Roth</t>
+        </is>
+      </c>
+      <c r="X372" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>145823</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://larssoreide.no</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>post@larssoreide.no</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr"/>
+      <c r="P373" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>945663855</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="inlineStr"/>
+      <c r="S373" s="2" t="inlineStr"/>
+      <c r="T373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
+      <c r="W373" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide</t>
+        </is>
+      </c>
+      <c r="X373" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lars-s%C3%B8reide-393732174/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr"/>
+      <c r="P374" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="inlineStr"/>
+      <c r="S374" s="2" t="inlineStr"/>
+      <c r="T374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr"/>
+      <c r="W374" s="2" t="inlineStr">
+        <is>
+          <t>Jan Erik</t>
+        </is>
+      </c>
+      <c r="X374" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr"/>
+      <c r="P375" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr"/>
+      <c r="S375" s="2" t="inlineStr"/>
+      <c r="T375" s="2" t="inlineStr"/>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
+      <c r="W375" s="2" t="inlineStr">
+        <is>
+          <t>Simen Syrrist</t>
+        </is>
+      </c>
+      <c r="X375" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA375" s="2" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>145839</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>6A Veitvetveien</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>0596</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>import@chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr"/>
+      <c r="P376" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>932088525</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="inlineStr"/>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61552797656796</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chrismidtunimport</t>
+        </is>
+      </c>
+      <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr"/>
+      <c r="W376" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun</t>
+        </is>
+      </c>
+      <c r="X376" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr"/>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr"/>
+      <c r="P377" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="inlineStr"/>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr"/>
+      <c r="W377" s="2" t="inlineStr">
+        <is>
+          <t>Pål Bertil</t>
+        </is>
+      </c>
+      <c r="X377" s="2" t="inlineStr">
+        <is>
+          <t>Chairman And Owner</t>
+        </is>
+      </c>
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/p%C3%A5l-bertil-eide-69414610b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr"/>
+      <c r="P378" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="inlineStr"/>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr">
+        <is>
+          <t>Olav Martens</t>
+        </is>
+      </c>
+      <c r="X378" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/olav-martens-solli-2b0221121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>102275</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>134 Randabergveien</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>http://www.terroir.no</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr"/>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>torleiv@terroir.no</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr"/>
+      <c r="P379" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>976307356</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="inlineStr"/>
+      <c r="S379" s="2" t="inlineStr"/>
+      <c r="T379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr"/>
+      <c r="W379" s="2" t="inlineStr">
+        <is>
+          <t>Torleiv B.</t>
+        </is>
+      </c>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>Owner, Ceo</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr"/>
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/torleiv-middelthon-81101528/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA379"/>
+  <dimension ref="A1:AA396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41343,6 +41343,1663 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>145850</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>2 Gustavs gate</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dogowines.com</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>danjoakim@dogowines.no</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr"/>
+      <c r="P380" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>926421867</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="inlineStr"/>
+      <c r="S380" s="2" t="inlineStr"/>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dogowines/</t>
+        </is>
+      </c>
+      <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr"/>
+      <c r="W380" s="2" t="inlineStr">
+        <is>
+          <t>Dan Joakim</t>
+        </is>
+      </c>
+      <c r="X380" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dan-joakim-ask-nessa-0918171b</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr"/>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
+      <c r="W381" s="2" t="inlineStr">
+        <is>
+          <t>Dag Robert</t>
+        </is>
+      </c>
+      <c r="X381" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dag-robert-s%C3%B8r%C3%A5s-077aa3a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr">
+        <is>
+          <t>Carl Frimanslund</t>
+        </is>
+      </c>
+      <c r="X382" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carl-frimanslund/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>45175</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Sandvika</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>2A Jongsåsveien</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr"/>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>espen@bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr"/>
+      <c r="P383" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>922253935</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr"/>
+      <c r="S383" s="2" t="inlineStr"/>
+      <c r="T383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr">
+        <is>
+          <t>Espen Hoel</t>
+        </is>
+      </c>
+      <c r="X383" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/espen-hoel-80494a3b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O384" s="2" t="inlineStr"/>
+      <c r="P384" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr"/>
+      <c r="S384" s="2" t="inlineStr"/>
+      <c r="T384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr"/>
+      <c r="W384" s="2" t="inlineStr">
+        <is>
+          <t>Richard Eikeland</t>
+        </is>
+      </c>
+      <c r="X384" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Logistics</t>
+        </is>
+      </c>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA384" s="2" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr"/>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr"/>
+      <c r="S385" s="2" t="inlineStr"/>
+      <c r="T385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr"/>
+      <c r="W385" s="2" t="inlineStr">
+        <is>
+          <t>Peter Dorstad</t>
+        </is>
+      </c>
+      <c r="X385" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Product Manager</t>
+        </is>
+      </c>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-d%C3%B8rstad-526782138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>145830</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Viken</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>5 Orreveien</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>0789</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.interlope.no</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>wine@interlope.no</t>
+        </is>
+      </c>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 49 02 20</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>998058929</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr"/>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/interlope.wine/</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr"/>
+      <c r="W386" s="2" t="inlineStr">
+        <is>
+          <t>Ingar Grønstad</t>
+        </is>
+      </c>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr"/>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O387" s="2" t="inlineStr"/>
+      <c r="P387" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S387" s="2" t="inlineStr"/>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr">
+        <is>
+          <t>Giacomo Caramaschi</t>
+        </is>
+      </c>
+      <c r="X387" s="2" t="inlineStr">
+        <is>
+          <t>Co-Owner</t>
+        </is>
+      </c>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O388" s="2" t="inlineStr"/>
+      <c r="P388" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S388" s="2" t="inlineStr"/>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Colsenet</t>
+        </is>
+      </c>
+      <c r="X388" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Co-owner</t>
+        </is>
+      </c>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benjamin-colsenet-34bb472b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O389" s="2" t="inlineStr"/>
+      <c r="P389" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S389" s="2" t="inlineStr"/>
+      <c r="T389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan D. Roth</t>
+        </is>
+      </c>
+      <c r="X389" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>145823</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://larssoreide.no</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>post@larssoreide.no</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr"/>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>945663855</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr"/>
+      <c r="S390" s="2" t="inlineStr"/>
+      <c r="T390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide</t>
+        </is>
+      </c>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lars-s%C3%B8reide-393732174/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr"/>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr"/>
+      <c r="S391" s="2" t="inlineStr"/>
+      <c r="T391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr">
+        <is>
+          <t>Jan Erik</t>
+        </is>
+      </c>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA391" s="2" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O392" s="2" t="inlineStr"/>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr"/>
+      <c r="S392" s="2" t="inlineStr"/>
+      <c r="T392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr">
+        <is>
+          <t>Simen Syrrist</t>
+        </is>
+      </c>
+      <c r="X392" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA392" s="2" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>145839</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>6A Veitvetveien</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>0596</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>import@chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="O393" s="2" t="inlineStr"/>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>932088525</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr"/>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61552797656796</t>
+        </is>
+      </c>
+      <c r="T393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chrismidtunimport</t>
+        </is>
+      </c>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun</t>
+        </is>
+      </c>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O394" s="2" t="inlineStr"/>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr"/>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr">
+        <is>
+          <t>Pål Bertil</t>
+        </is>
+      </c>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>Chairman And Owner</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr"/>
+      <c r="Z394" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/p%C3%A5l-bertil-eide-69414610b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr"/>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O395" s="2" t="inlineStr"/>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr"/>
+      <c r="S395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr">
+        <is>
+          <t>Olav Martens</t>
+        </is>
+      </c>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/olav-martens-solli-2b0221121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>102275</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>134 Randabergveien</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>http://www.terroir.no</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>torleiv@terroir.no</t>
+        </is>
+      </c>
+      <c r="O396" s="2" t="inlineStr"/>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>976307356</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr"/>
+      <c r="S396" s="2" t="inlineStr"/>
+      <c r="T396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr">
+        <is>
+          <t>Torleiv B.</t>
+        </is>
+      </c>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>Owner, Ceo</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/torleiv-middelthon-81101528/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA396"/>
+  <dimension ref="A1:AA413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -43000,6 +43000,1663 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>145850</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>2 Gustavs gate</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dogowines.com</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr"/>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr">
+        <is>
+          <t>danjoakim@dogowines.no</t>
+        </is>
+      </c>
+      <c r="O397" s="2" t="inlineStr"/>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>926421867</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr"/>
+      <c r="S397" s="2" t="inlineStr"/>
+      <c r="T397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dogowines/</t>
+        </is>
+      </c>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr">
+        <is>
+          <t>Dan Joakim</t>
+        </is>
+      </c>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr"/>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dan-joakim-ask-nessa-0918171b</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O398" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr">
+        <is>
+          <t>Dag Robert</t>
+        </is>
+      </c>
+      <c r="X398" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y398" s="2" t="inlineStr"/>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dag-robert-s%C3%B8r%C3%A5s-077aa3a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr"/>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O399" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P399" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr">
+        <is>
+          <t>Carl Frimanslund</t>
+        </is>
+      </c>
+      <c r="X399" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carl-frimanslund/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>45175</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Sandvika</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>2A Jongsåsveien</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>https://bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr">
+        <is>
+          <t>espen@bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="O400" s="2" t="inlineStr"/>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>922253935</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr"/>
+      <c r="S400" s="2" t="inlineStr"/>
+      <c r="T400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr">
+        <is>
+          <t>Espen Hoel</t>
+        </is>
+      </c>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/espen-hoel-80494a3b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr"/>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr"/>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr"/>
+      <c r="S401" s="2" t="inlineStr"/>
+      <c r="T401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
+      <c r="W401" s="2" t="inlineStr">
+        <is>
+          <t>Richard Eikeland</t>
+        </is>
+      </c>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Logistics</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA401" s="2" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O402" s="2" t="inlineStr"/>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr"/>
+      <c r="S402" s="2" t="inlineStr"/>
+      <c r="T402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr">
+        <is>
+          <t>Peter Dorstad</t>
+        </is>
+      </c>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Product Manager</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-d%C3%B8rstad-526782138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>145830</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Viken</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>5 Orreveien</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>0789</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.interlope.no</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr"/>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>wine@interlope.no</t>
+        </is>
+      </c>
+      <c r="O403" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 49 02 20</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>998058929</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr"/>
+      <c r="S403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/interlope.wine/</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="inlineStr">
+        <is>
+          <t>Ingar Grønstad</t>
+        </is>
+      </c>
+      <c r="X403" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O404" s="2" t="inlineStr"/>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S404" s="2" t="inlineStr"/>
+      <c r="T404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr">
+        <is>
+          <t>Giacomo Caramaschi</t>
+        </is>
+      </c>
+      <c r="X404" s="2" t="inlineStr">
+        <is>
+          <t>Co-Owner</t>
+        </is>
+      </c>
+      <c r="Y404" s="2" t="inlineStr"/>
+      <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr"/>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr"/>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O405" s="2" t="inlineStr"/>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S405" s="2" t="inlineStr"/>
+      <c r="T405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Colsenet</t>
+        </is>
+      </c>
+      <c r="X405" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Co-owner</t>
+        </is>
+      </c>
+      <c r="Y405" s="2" t="inlineStr"/>
+      <c r="Z405" s="2" t="inlineStr"/>
+      <c r="AA405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benjamin-colsenet-34bb472b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O406" s="2" t="inlineStr"/>
+      <c r="P406" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S406" s="2" t="inlineStr"/>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan D. Roth</t>
+        </is>
+      </c>
+      <c r="X406" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y406" s="2" t="inlineStr"/>
+      <c r="Z406" s="2" t="inlineStr"/>
+      <c r="AA406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>145823</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>https://larssoreide.no</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr"/>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr"/>
+      <c r="N407" s="2" t="inlineStr">
+        <is>
+          <t>post@larssoreide.no</t>
+        </is>
+      </c>
+      <c r="O407" s="2" t="inlineStr"/>
+      <c r="P407" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>945663855</t>
+        </is>
+      </c>
+      <c r="R407" s="2" t="inlineStr"/>
+      <c r="S407" s="2" t="inlineStr"/>
+      <c r="T407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide</t>
+        </is>
+      </c>
+      <c r="X407" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y407" s="2" t="inlineStr"/>
+      <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lars-s%C3%B8reide-393732174/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O408" s="2" t="inlineStr"/>
+      <c r="P408" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R408" s="2" t="inlineStr"/>
+      <c r="S408" s="2" t="inlineStr"/>
+      <c r="T408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="inlineStr"/>
+      <c r="V408" s="2" t="inlineStr"/>
+      <c r="W408" s="2" t="inlineStr">
+        <is>
+          <t>Jan Erik</t>
+        </is>
+      </c>
+      <c r="X408" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y408" s="2" t="inlineStr"/>
+      <c r="Z408" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA408" s="2" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr"/>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="inlineStr"/>
+      <c r="N409" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O409" s="2" t="inlineStr"/>
+      <c r="P409" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q409" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R409" s="2" t="inlineStr"/>
+      <c r="S409" s="2" t="inlineStr"/>
+      <c r="T409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr"/>
+      <c r="W409" s="2" t="inlineStr">
+        <is>
+          <t>Simen Syrrist</t>
+        </is>
+      </c>
+      <c r="X409" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y409" s="2" t="inlineStr"/>
+      <c r="Z409" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA409" s="2" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>145839</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>6A Veitvetveien</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>0596</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr">
+        <is>
+          <t>import@chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="O410" s="2" t="inlineStr"/>
+      <c r="P410" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>932088525</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="inlineStr"/>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61552797656796</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chrismidtunimport</t>
+        </is>
+      </c>
+      <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr"/>
+      <c r="W410" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun</t>
+        </is>
+      </c>
+      <c r="X410" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y410" s="2" t="inlineStr"/>
+      <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr"/>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr"/>
+      <c r="N411" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O411" s="2" t="inlineStr"/>
+      <c r="P411" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="inlineStr"/>
+      <c r="S411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr"/>
+      <c r="W411" s="2" t="inlineStr">
+        <is>
+          <t>Pål Bertil</t>
+        </is>
+      </c>
+      <c r="X411" s="2" t="inlineStr">
+        <is>
+          <t>Chairman And Owner</t>
+        </is>
+      </c>
+      <c r="Y411" s="2" t="inlineStr"/>
+      <c r="Z411" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/p%C3%A5l-bertil-eide-69414610b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr"/>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr"/>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="inlineStr">
+        <is>
+          <t>Olav Martens</t>
+        </is>
+      </c>
+      <c r="X412" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y412" s="2" t="inlineStr"/>
+      <c r="Z412" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/olav-martens-solli-2b0221121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>102275</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>134 Randabergveien</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>http://www.terroir.no</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr"/>
+      <c r="K413" s="2" t="inlineStr"/>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr"/>
+      <c r="N413" s="2" t="inlineStr">
+        <is>
+          <t>torleiv@terroir.no</t>
+        </is>
+      </c>
+      <c r="O413" s="2" t="inlineStr"/>
+      <c r="P413" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>976307356</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="inlineStr"/>
+      <c r="S413" s="2" t="inlineStr"/>
+      <c r="T413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr">
+        <is>
+          <t>Torleiv B.</t>
+        </is>
+      </c>
+      <c r="X413" s="2" t="inlineStr">
+        <is>
+          <t>Owner, Ceo</t>
+        </is>
+      </c>
+      <c r="Y413" s="2" t="inlineStr"/>
+      <c r="Z413" s="2" t="inlineStr"/>
+      <c r="AA413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/torleiv-middelthon-81101528/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA413"/>
+  <dimension ref="A1:AA430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -44657,6 +44657,1663 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>Dogo Wines As</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>145850</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>2 Gustavs gate</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dogowines.com</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr"/>
+      <c r="K414" s="2" t="inlineStr"/>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="inlineStr"/>
+      <c r="N414" s="2" t="inlineStr">
+        <is>
+          <t>danjoakim@dogowines.no</t>
+        </is>
+      </c>
+      <c r="O414" s="2" t="inlineStr"/>
+      <c r="P414" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>926421867</t>
+        </is>
+      </c>
+      <c r="R414" s="2" t="inlineStr"/>
+      <c r="S414" s="2" t="inlineStr"/>
+      <c r="T414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dogowines/</t>
+        </is>
+      </c>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr">
+        <is>
+          <t>Dan Joakim</t>
+        </is>
+      </c>
+      <c r="X414" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y414" s="2" t="inlineStr"/>
+      <c r="Z414" s="2" t="inlineStr"/>
+      <c r="AA414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dan-joakim-ask-nessa-0918171b</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr"/>
+      <c r="K415" s="2" t="inlineStr"/>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="inlineStr"/>
+      <c r="N415" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O415" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr">
+        <is>
+          <t>Dag Robert</t>
+        </is>
+      </c>
+      <c r="X415" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y415" s="2" t="inlineStr"/>
+      <c r="Z415" s="2" t="inlineStr"/>
+      <c r="AA415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dag-robert-s%C3%B8r%C3%A5s-077aa3a6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>Måkestad Engros As</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>145821</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>Bergen</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Vestland</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>2 Lønningshaugen</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>http://www.makestadengros.no, https://www.makestad.no</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr"/>
+      <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="inlineStr"/>
+      <c r="N416" s="2" t="inlineStr">
+        <is>
+          <t>firmapost@makestad.no</t>
+        </is>
+      </c>
+      <c r="O416" s="2" t="inlineStr">
+        <is>
+          <t>+47 55 14 10 00</t>
+        </is>
+      </c>
+      <c r="P416" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q416" s="2" t="inlineStr">
+        <is>
+          <t>981521935</t>
+        </is>
+      </c>
+      <c r="R416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-kestad-engros/</t>
+        </is>
+      </c>
+      <c r="S416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TLMakestad</t>
+        </is>
+      </c>
+      <c r="T416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/makestad.no</t>
+        </is>
+      </c>
+      <c r="U416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr">
+        <is>
+          <t>Carl Frimanslund</t>
+        </is>
+      </c>
+      <c r="X416" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y416" s="2" t="inlineStr"/>
+      <c r="Z416" s="2" t="inlineStr"/>
+      <c r="AA416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carl-frimanslund/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>Bekkekjellern</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>45175</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>Sandvika</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>2A Jongsåsveien</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>https://bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr"/>
+      <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="inlineStr"/>
+      <c r="N417" s="2" t="inlineStr">
+        <is>
+          <t>espen@bekkekjellern.no</t>
+        </is>
+      </c>
+      <c r="O417" s="2" t="inlineStr"/>
+      <c r="P417" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>922253935</t>
+        </is>
+      </c>
+      <c r="R417" s="2" t="inlineStr"/>
+      <c r="S417" s="2" t="inlineStr"/>
+      <c r="T417" s="2" t="inlineStr"/>
+      <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="inlineStr"/>
+      <c r="W417" s="2" t="inlineStr">
+        <is>
+          <t>Espen Hoel</t>
+        </is>
+      </c>
+      <c r="X417" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y417" s="2" t="inlineStr"/>
+      <c r="Z417" s="2" t="inlineStr"/>
+      <c r="AA417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/espen-hoel-80494a3b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr"/>
+      <c r="K418" s="2" t="inlineStr"/>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="inlineStr"/>
+      <c r="N418" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O418" s="2" t="inlineStr"/>
+      <c r="P418" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q418" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R418" s="2" t="inlineStr"/>
+      <c r="S418" s="2" t="inlineStr"/>
+      <c r="T418" s="2" t="inlineStr"/>
+      <c r="U418" s="2" t="inlineStr"/>
+      <c r="V418" s="2" t="inlineStr"/>
+      <c r="W418" s="2" t="inlineStr">
+        <is>
+          <t>Richard Eikeland</t>
+        </is>
+      </c>
+      <c r="X418" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Logistics</t>
+        </is>
+      </c>
+      <c r="Y418" s="2" t="inlineStr"/>
+      <c r="Z418" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA418" s="2" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>Dørstad Grapes As</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>145837</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>Horten</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Vestfold</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>8a Briskestien</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://dorstad.no</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr"/>
+      <c r="K419" s="2" t="inlineStr"/>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="inlineStr"/>
+      <c r="N419" s="2" t="inlineStr">
+        <is>
+          <t>grapes@dorstad.no</t>
+        </is>
+      </c>
+      <c r="O419" s="2" t="inlineStr"/>
+      <c r="P419" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q419" s="2" t="inlineStr">
+        <is>
+          <t>920052118</t>
+        </is>
+      </c>
+      <c r="R419" s="2" t="inlineStr"/>
+      <c r="S419" s="2" t="inlineStr"/>
+      <c r="T419" s="2" t="inlineStr"/>
+      <c r="U419" s="2" t="inlineStr"/>
+      <c r="V419" s="2" t="inlineStr"/>
+      <c r="W419" s="2" t="inlineStr">
+        <is>
+          <t>Peter Dorstad</t>
+        </is>
+      </c>
+      <c r="X419" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Product Manager</t>
+        </is>
+      </c>
+      <c r="Y419" s="2" t="inlineStr"/>
+      <c r="Z419" s="2" t="inlineStr"/>
+      <c r="AA419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-d%C3%B8rstad-526782138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>Interlope As</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>145830</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Viken</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>5 Orreveien</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>0789</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.interlope.no</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr"/>
+      <c r="K420" s="2" t="inlineStr"/>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="inlineStr"/>
+      <c r="N420" s="2" t="inlineStr">
+        <is>
+          <t>wine@interlope.no</t>
+        </is>
+      </c>
+      <c r="O420" s="2" t="inlineStr">
+        <is>
+          <t>+47 22 49 02 20</t>
+        </is>
+      </c>
+      <c r="P420" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q420" s="2" t="inlineStr">
+        <is>
+          <t>998058929</t>
+        </is>
+      </c>
+      <c r="R420" s="2" t="inlineStr"/>
+      <c r="S420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/interlope.wine/</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="inlineStr"/>
+      <c r="U420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="inlineStr"/>
+      <c r="W420" s="2" t="inlineStr">
+        <is>
+          <t>Ingar Grønstad</t>
+        </is>
+      </c>
+      <c r="X420" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y420" s="2" t="inlineStr"/>
+      <c r="Z420" s="2" t="inlineStr"/>
+      <c r="AA420" s="2" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr"/>
+      <c r="K421" s="2" t="inlineStr"/>
+      <c r="L421" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="inlineStr"/>
+      <c r="N421" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O421" s="2" t="inlineStr"/>
+      <c r="P421" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q421" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S421" s="2" t="inlineStr"/>
+      <c r="T421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="inlineStr"/>
+      <c r="W421" s="2" t="inlineStr">
+        <is>
+          <t>Giacomo Caramaschi</t>
+        </is>
+      </c>
+      <c r="X421" s="2" t="inlineStr">
+        <is>
+          <t>Co-Owner</t>
+        </is>
+      </c>
+      <c r="Y421" s="2" t="inlineStr"/>
+      <c r="Z421" s="2" t="inlineStr"/>
+      <c r="AA421" s="2" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr"/>
+      <c r="K422" s="2" t="inlineStr"/>
+      <c r="L422" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="inlineStr"/>
+      <c r="N422" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O422" s="2" t="inlineStr"/>
+      <c r="P422" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q422" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S422" s="2" t="inlineStr"/>
+      <c r="T422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U422" s="2" t="inlineStr"/>
+      <c r="V422" s="2" t="inlineStr"/>
+      <c r="W422" s="2" t="inlineStr">
+        <is>
+          <t>Benjamin Colsenet</t>
+        </is>
+      </c>
+      <c r="X422" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Co-owner</t>
+        </is>
+      </c>
+      <c r="Y422" s="2" t="inlineStr"/>
+      <c r="Z422" s="2" t="inlineStr"/>
+      <c r="AA422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benjamin-colsenet-34bb472b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>Le Bambocheur As</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>145825</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>85A Vetlandsveien</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>0685</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr"/>
+      <c r="K423" s="2" t="inlineStr"/>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="inlineStr"/>
+      <c r="N423" s="2" t="inlineStr">
+        <is>
+          <t>benjamin@lebambocheur.no</t>
+        </is>
+      </c>
+      <c r="O423" s="2" t="inlineStr"/>
+      <c r="P423" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>927957558</t>
+        </is>
+      </c>
+      <c r="R423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/le-bambocheur-as/</t>
+        </is>
+      </c>
+      <c r="S423" s="2" t="inlineStr"/>
+      <c r="T423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lebambocheur</t>
+        </is>
+      </c>
+      <c r="U423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="inlineStr"/>
+      <c r="W423" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan D. Roth</t>
+        </is>
+      </c>
+      <c r="X423" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner &amp; Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y423" s="2" t="inlineStr"/>
+      <c r="Z423" s="2" t="inlineStr"/>
+      <c r="AA423" s="2" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide As</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>145823</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Telemark</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Bolkesjø</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>https://larssoreide.no</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr"/>
+      <c r="K424" s="2" t="inlineStr"/>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="inlineStr"/>
+      <c r="N424" s="2" t="inlineStr">
+        <is>
+          <t>post@larssoreide.no</t>
+        </is>
+      </c>
+      <c r="O424" s="2" t="inlineStr"/>
+      <c r="P424" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q424" s="2" t="inlineStr">
+        <is>
+          <t>945663855</t>
+        </is>
+      </c>
+      <c r="R424" s="2" t="inlineStr"/>
+      <c r="S424" s="2" t="inlineStr"/>
+      <c r="T424" s="2" t="inlineStr"/>
+      <c r="U424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="inlineStr"/>
+      <c r="W424" s="2" t="inlineStr">
+        <is>
+          <t>Lars Søreide</t>
+        </is>
+      </c>
+      <c r="X424" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y424" s="2" t="inlineStr"/>
+      <c r="Z424" s="2" t="inlineStr"/>
+      <c r="AA424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lars-s%C3%B8reide-393732174/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr"/>
+      <c r="K425" s="2" t="inlineStr"/>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="inlineStr"/>
+      <c r="N425" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O425" s="2" t="inlineStr"/>
+      <c r="P425" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R425" s="2" t="inlineStr"/>
+      <c r="S425" s="2" t="inlineStr"/>
+      <c r="T425" s="2" t="inlineStr"/>
+      <c r="U425" s="2" t="inlineStr"/>
+      <c r="V425" s="2" t="inlineStr"/>
+      <c r="W425" s="2" t="inlineStr">
+        <is>
+          <t>Jan Erik</t>
+        </is>
+      </c>
+      <c r="X425" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y425" s="2" t="inlineStr"/>
+      <c r="Z425" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA425" s="2" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>J Island Wine As</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Østfold</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>13 Åslia</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jisland.wine</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr"/>
+      <c r="K426" s="2" t="inlineStr"/>
+      <c r="L426" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="inlineStr"/>
+      <c r="N426" s="2" t="inlineStr">
+        <is>
+          <t>jeb@jisland.wine</t>
+        </is>
+      </c>
+      <c r="O426" s="2" t="inlineStr"/>
+      <c r="P426" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q426" s="2" t="inlineStr">
+        <is>
+          <t>919814268</t>
+        </is>
+      </c>
+      <c r="R426" s="2" t="inlineStr"/>
+      <c r="S426" s="2" t="inlineStr"/>
+      <c r="T426" s="2" t="inlineStr"/>
+      <c r="U426" s="2" t="inlineStr"/>
+      <c r="V426" s="2" t="inlineStr"/>
+      <c r="W426" s="2" t="inlineStr">
+        <is>
+          <t>Simen Syrrist</t>
+        </is>
+      </c>
+      <c r="X426" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y426" s="2" t="inlineStr"/>
+      <c r="Z426" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA426" s="2" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun Import As</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>145839</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>6A Veitvetveien</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>0596</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr"/>
+      <c r="K427" s="2" t="inlineStr"/>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="inlineStr"/>
+      <c r="N427" s="2" t="inlineStr">
+        <is>
+          <t>import@chrismidtun.com</t>
+        </is>
+      </c>
+      <c r="O427" s="2" t="inlineStr"/>
+      <c r="P427" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>932088525</t>
+        </is>
+      </c>
+      <c r="R427" s="2" t="inlineStr"/>
+      <c r="S427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61552797656796</t>
+        </is>
+      </c>
+      <c r="T427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chrismidtunimport</t>
+        </is>
+      </c>
+      <c r="U427" s="2" t="inlineStr"/>
+      <c r="V427" s="2" t="inlineStr"/>
+      <c r="W427" s="2" t="inlineStr">
+        <is>
+          <t>Chris Midtun</t>
+        </is>
+      </c>
+      <c r="X427" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y427" s="2" t="inlineStr"/>
+      <c r="Z427" s="2" t="inlineStr"/>
+      <c r="AA427" s="2" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr"/>
+      <c r="K428" s="2" t="inlineStr"/>
+      <c r="L428" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="inlineStr"/>
+      <c r="N428" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O428" s="2" t="inlineStr"/>
+      <c r="P428" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q428" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R428" s="2" t="inlineStr"/>
+      <c r="S428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T428" s="2" t="inlineStr"/>
+      <c r="U428" s="2" t="inlineStr"/>
+      <c r="V428" s="2" t="inlineStr"/>
+      <c r="W428" s="2" t="inlineStr">
+        <is>
+          <t>Pål Bertil</t>
+        </is>
+      </c>
+      <c r="X428" s="2" t="inlineStr">
+        <is>
+          <t>Chairman And Owner</t>
+        </is>
+      </c>
+      <c r="Y428" s="2" t="inlineStr"/>
+      <c r="Z428" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/p%C3%A5l-bertil-eide-69414610b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>Bertil &amp; Martens As</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>145842</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>Otta</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Innlandet</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>8 Ottbragdgata</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr"/>
+      <c r="K429" s="2" t="inlineStr"/>
+      <c r="L429" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="inlineStr"/>
+      <c r="N429" s="2" t="inlineStr">
+        <is>
+          <t>post@bertilogmartens.no</t>
+        </is>
+      </c>
+      <c r="O429" s="2" t="inlineStr"/>
+      <c r="P429" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q429" s="2" t="inlineStr">
+        <is>
+          <t>814467082</t>
+        </is>
+      </c>
+      <c r="R429" s="2" t="inlineStr"/>
+      <c r="S429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bertilogmartens/</t>
+        </is>
+      </c>
+      <c r="T429" s="2" t="inlineStr"/>
+      <c r="U429" s="2" t="inlineStr"/>
+      <c r="V429" s="2" t="inlineStr"/>
+      <c r="W429" s="2" t="inlineStr">
+        <is>
+          <t>Olav Martens</t>
+        </is>
+      </c>
+      <c r="X429" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y429" s="2" t="inlineStr"/>
+      <c r="Z429" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/olav-martens-solli-2b0221121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>TERROIR AS</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>102275</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>134 Randabergveien</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>http://www.terroir.no</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr"/>
+      <c r="K430" s="2" t="inlineStr"/>
+      <c r="L430" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="inlineStr"/>
+      <c r="N430" s="2" t="inlineStr">
+        <is>
+          <t>torleiv@terroir.no</t>
+        </is>
+      </c>
+      <c r="O430" s="2" t="inlineStr"/>
+      <c r="P430" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q430" s="2" t="inlineStr">
+        <is>
+          <t>976307356</t>
+        </is>
+      </c>
+      <c r="R430" s="2" t="inlineStr"/>
+      <c r="S430" s="2" t="inlineStr"/>
+      <c r="T430" s="2" t="inlineStr"/>
+      <c r="U430" s="2" t="inlineStr"/>
+      <c r="V430" s="2" t="inlineStr"/>
+      <c r="W430" s="2" t="inlineStr">
+        <is>
+          <t>Torleiv B.</t>
+        </is>
+      </c>
+      <c r="X430" s="2" t="inlineStr">
+        <is>
+          <t>Owner, Ceo</t>
+        </is>
+      </c>
+      <c r="Y430" s="2" t="inlineStr"/>
+      <c r="Z430" s="2" t="inlineStr"/>
+      <c r="AA430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/torleiv-middelthon-81101528/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
